--- a/selenium-java/src/test/resources/Data.xlsx
+++ b/selenium-java/src/test/resources/Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\eclipse-workspace\selenium-java\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\git\CRM_project\selenium-java\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E70E672-03E2-4786-85F1-22D0B629E9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AC1F7F-596A-41F2-841B-EB3AA85E4235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>TechNova Solutions</t>
   </si>
@@ -344,7 +344,46 @@
     <t>Mobail no</t>
   </si>
   <si>
-    <t>9876501001</t>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>9123456780</t>
+  </si>
+  <si>
+    <t>9988776655</t>
+  </si>
+  <si>
+    <t>9012345678</t>
+  </si>
+  <si>
+    <t>8899776655</t>
+  </si>
+  <si>
+    <t>9345678901</t>
+  </si>
+  <si>
+    <t>8765432109</t>
+  </si>
+  <si>
+    <t>9654321078</t>
+  </si>
+  <si>
+    <t>7890123456</t>
+  </si>
+  <si>
+    <t>8098765432</t>
   </si>
 </sst>
 </file>
@@ -424,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -433,10 +472,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,7 +772,7 @@
       <c r="C1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -774,8 +810,8 @@
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3">
-        <v>9876501002</v>
+      <c r="D3" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
@@ -793,8 +829,8 @@
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3">
-        <v>9876501003</v>
+      <c r="D4" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
@@ -812,8 +848,8 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3">
-        <v>9876501004</v>
+      <c r="D5" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -831,8 +867,8 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3">
-        <v>9876501005</v>
+      <c r="D6" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -850,8 +886,8 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3">
-        <v>9876501006</v>
+      <c r="D7" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>21</v>
@@ -869,8 +905,8 @@
       <c r="C8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="3">
-        <v>9876501007</v>
+      <c r="D8" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>24</v>
@@ -888,8 +924,8 @@
       <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="3">
-        <v>9876501008</v>
+      <c r="D9" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -907,8 +943,8 @@
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="3">
-        <v>9876501009</v>
+      <c r="D10" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>30</v>
@@ -926,8 +962,8 @@
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="3">
-        <v>9876501010</v>
+      <c r="D11" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>33</v>
@@ -942,16 +978,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56A4213A-43DB-49CD-B1B0-43C1027311EC}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>101</v>
       </c>
@@ -967,8 +1004,11 @@
       <c r="E1" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
@@ -984,8 +1024,11 @@
       <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -1001,8 +1044,11 @@
       <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
@@ -1018,8 +1064,11 @@
       <c r="E4" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -1035,8 +1084,11 @@
       <c r="E5" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>50</v>
       </c>
@@ -1052,8 +1104,11 @@
       <c r="E6" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>54</v>
       </c>
@@ -1069,8 +1124,11 @@
       <c r="E7" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
@@ -1086,8 +1144,11 @@
       <c r="E8" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1103,8 +1164,11 @@
       <c r="E9" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>65</v>
       </c>
@@ -1120,8 +1184,11 @@
       <c r="E10" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>69</v>
       </c>
@@ -1136,6 +1203,9 @@
       </c>
       <c r="E11" s="3" t="s">
         <v>72</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1218,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -1185,8 +1255,8 @@
       <c r="D2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="5">
-        <v>9876543210</v>
+      <c r="E2" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1202,8 +1272,8 @@
       <c r="D3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="5">
-        <v>9123456780</v>
+      <c r="E3" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1219,8 +1289,8 @@
       <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5">
-        <v>9988776655</v>
+      <c r="E4" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1236,8 +1306,8 @@
       <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="5">
-        <v>9012345678</v>
+      <c r="E5" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,8 +1323,8 @@
       <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5">
-        <v>8899776655</v>
+      <c r="E6" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,8 +1340,8 @@
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="5">
-        <v>9345678901</v>
+      <c r="E7" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1287,8 +1357,8 @@
       <c r="D8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="5">
-        <v>8765432109</v>
+      <c r="E8" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1304,8 +1374,8 @@
       <c r="D9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="5">
-        <v>9654321078</v>
+      <c r="E9" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,8 +1391,8 @@
       <c r="D10" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="5">
-        <v>7890123456</v>
+      <c r="E10" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,8 +1408,8 @@
       <c r="D11" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="5">
-        <v>8098765432</v>
+      <c r="E11" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-java/src/test/resources/Data.xlsx
+++ b/selenium-java/src/test/resources/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\git\CRM_project\selenium-java\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AC1F7F-596A-41F2-841B-EB3AA85E4235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A58AA9-0EE1-4E87-B0D7-A9ACC616E950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5796" yWindow="108" windowWidth="11676" windowHeight="12864" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ORGname" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
   <si>
     <t>TechNova Solutions</t>
   </si>
@@ -345,18 +345,6 @@
   </si>
   <si>
     <t>9876543210</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
   </si>
   <si>
     <t>9123456780</t>
@@ -811,7 +799,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
@@ -830,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
@@ -849,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -868,7 +856,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -887,7 +875,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>21</v>
@@ -906,7 +894,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>24</v>
@@ -925,7 +913,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -944,7 +932,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>30</v>
@@ -963,7 +951,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>33</v>
@@ -1045,7 +1033,7 @@
         <v>41</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1065,7 +1053,7 @@
         <v>45</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1085,7 +1073,7 @@
         <v>49</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1105,7 +1093,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1125,7 +1113,7 @@
         <v>56</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1145,7 +1133,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1165,7 +1153,7 @@
         <v>64</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1185,7 +1173,7 @@
         <v>68</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1205,7 +1193,7 @@
         <v>72</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1261,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1290,7 +1278,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1307,7 +1295,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1324,7 +1312,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1341,7 +1329,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1358,7 +1346,7 @@
         <v>86</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1375,7 +1363,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1392,7 +1380,7 @@
         <v>91</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1409,7 +1397,7 @@
         <v>93</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
